--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.98246498382319</v>
+        <v>5.034650559871269</v>
       </c>
       <c r="D2" t="n">
-        <v>28.38196993481808</v>
+        <v>4.612070114407939</v>
       </c>
       <c r="E2" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F2" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.79991381863189</v>
+        <v>2.892485995527681</v>
       </c>
       <c r="D3" t="n">
-        <v>17.65901654842932</v>
+        <v>2.869590189119764</v>
       </c>
       <c r="E3" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F3" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.6065366822801</v>
+        <v>2.373562210870517</v>
       </c>
       <c r="D4" t="n">
-        <v>16.25762914023503</v>
+        <v>2.641864735288193</v>
       </c>
       <c r="E4" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F4" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.18326169792954</v>
+        <v>2.629780025913551</v>
       </c>
       <c r="D5" t="n">
-        <v>23.37511018030141</v>
+        <v>3.79845540429898</v>
       </c>
       <c r="E5" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F5" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.86876152794657</v>
+        <v>6.803673748291319</v>
       </c>
       <c r="D6" t="n">
-        <v>15.09966207323815</v>
+        <v>2.453695086901199</v>
       </c>
       <c r="E6" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F6" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.28604303637984</v>
+        <v>2.646481993411725</v>
       </c>
       <c r="D7" t="n">
-        <v>15.26383614552879</v>
+        <v>2.480373373648429</v>
       </c>
       <c r="E7" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F7" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.81531703779029</v>
+        <v>2.894989018640923</v>
       </c>
       <c r="D8" t="n">
-        <v>16.06186742042524</v>
+        <v>2.610053455819102</v>
       </c>
       <c r="E8" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F8" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.72863788250896</v>
+        <v>6.293403655907706</v>
       </c>
       <c r="D9" t="n">
-        <v>38.92341863491362</v>
+        <v>6.325055528173463</v>
       </c>
       <c r="E9" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F9" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30451623385989</v>
+        <v>5.899483888002233</v>
       </c>
       <c r="D10" t="n">
-        <v>33.18848900551419</v>
+        <v>5.393129463396055</v>
       </c>
       <c r="E10" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F10" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.54760945850597</v>
+        <v>4.963986537007219</v>
       </c>
       <c r="D11" t="n">
-        <v>17.10311485793552</v>
+        <v>2.779256164414522</v>
       </c>
       <c r="E11" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F11" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.52615675674094</v>
+        <v>2.035500472970403</v>
       </c>
       <c r="D12" t="n">
-        <v>9.427445895422107</v>
+        <v>1.531959958006092</v>
       </c>
       <c r="E12" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F12" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.07815740417947</v>
+        <v>1.962700578179164</v>
       </c>
       <c r="D13" t="n">
-        <v>19.85759469525711</v>
+        <v>3.22685913797928</v>
       </c>
       <c r="E13" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F13" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.39111243341694</v>
+        <v>7.051055770430254</v>
       </c>
       <c r="D14" t="n">
-        <v>7.375883324302658</v>
+        <v>1.198581040199182</v>
       </c>
       <c r="E14" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F14" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.2583112147984</v>
+        <v>5.241975572404741</v>
       </c>
       <c r="D15" t="n">
-        <v>21.19484191935996</v>
+        <v>3.444161811895994</v>
       </c>
       <c r="E15" t="n">
-        <v>11.13804046529225</v>
+        <v>1.809931575609991</v>
       </c>
       <c r="F15" t="n">
-        <v>8.349754768785674</v>
+        <v>1.356835149927672</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
